--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-2026-06-30.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-2026-06-30.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>06/30 10:22:52</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>940000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>114634.15</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>06/30 10:08:02</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>60240.96</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>羊美云</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>500000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>1440000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>174875.11</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>60240.96</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>174875.11</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-2026-06-30.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-2026-06-30.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/30 10:22:52</t>
+          <t>06/30 10:47:16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,17 +90,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>114634.15</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t/>
+          <t>耿振云</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -117,183 +117,225 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>06/30 10:22:52</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>940000</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>114634.15</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>06/30 10:08:02</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>60240.96</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>羊美云</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1440000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>174875.11</t>
+          <t>1720000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>208610.05</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>174875.11</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>208610.05</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-2026-06-30.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-2026-06-30.xlsx
@@ -283,59 +283,86 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>06/30 11:35:36</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>79000</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1720000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>208610.05</t>
+          <t>1720000</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>208610.05</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>79000</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>208610.05</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>129610.05</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-2026-06-30.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-2026-06-30.xlsx
@@ -286,83 +286,110 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>06/30 11:50:16</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>61000</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>06/30 11:35:36</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>79000</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1720000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>208610.05</t>
+          <t>1720000</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>79000</t>
+          <t>208610.05</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>140000</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>129610.05</t>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>68610.05</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-2026-06-30.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-2026-06-30.xlsx
@@ -286,12 +286,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>06/30 11:50:16</t>
+          <t>06/30 12:16:11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>61000</t>
+          <t>68610</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -301,7 +301,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -313,83 +313,110 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>06/30 11:50:16</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>61000</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>06/30 11:35:36</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>79000</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1720000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>208610.05</t>
+          <t>1720000</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>208610.05</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>208610</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>68610.05</t>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0.05</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-2026-06-30.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-2026-06-30.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/30 10:47:16</t>
+          <t>06/30 13:00:19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,12 +95,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>33734.94</t>
+          <t>38554.22</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>耿振云</t>
+          <t>李志伟</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06/30 10:22:52</t>
+          <t>06/30 10:47:16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,17 +132,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>114634.15</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t/>
+          <t>耿振云</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -159,166 +159,181 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>06/30 10:22:52</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>940000</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>114634.15</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>06/30 10:08:02</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>60240.96</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>羊美云</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>06/30 12:16:11</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>68610</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06/30 11:50:16</t>
+          <t>06/30 12:16:11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>61000</t>
+          <t>68610</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -328,7 +343,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -340,83 +355,110 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>06/30 11:50:16</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>61000</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>06/30 11:35:36</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>79000</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1720000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>208610.05</t>
+          <t>2040000</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>208610</t>
+          <t>247164.27</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>208610</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>0.05</t>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>38554.27</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-2026-06-30.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-2026-06-30.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/30 13:00:19</t>
+          <t>06/30 13:54:57</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,12 +95,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>38554.22</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>李志伟</t>
+          <t>马瑞昭</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06/30 10:47:16</t>
+          <t>06/30 13:00:19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,12 +137,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>33734.94</t>
+          <t>38554.22</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>耿振云</t>
+          <t>李志伟</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06/30 10:22:52</t>
+          <t>06/30 10:47:16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,17 +174,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>114634.15</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t/>
+          <t>耿振云</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -201,166 +201,181 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>06/30 10:22:52</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>940000</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>114634.15</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>06/30 10:08:02</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>60240.96</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>羊美云</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06/30 12:16:11</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>68610</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06/30 11:50:16</t>
+          <t>06/30 12:16:11</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>61000</t>
+          <t>68610</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -370,7 +385,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -382,83 +397,110 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>06/30 11:50:16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>61000</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>06/30 11:35:36</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>79000</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2040000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>247164.27</t>
+          <t>2320000</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>208610</t>
+          <t>280899.21</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>208610</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>38554.27</t>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>72289.21</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-2026-06-30.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-2026-06-30.xlsx
@@ -370,12 +370,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06/30 12:16:11</t>
+          <t>06/30 15:16:34</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>68610</t>
+          <t>72289</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -385,7 +385,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -397,12 +397,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06/30 11:50:16</t>
+          <t>06/30 12:16:11</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>61000</t>
+          <t>68610</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -412,7 +412,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -424,83 +424,110 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>06/30 11:50:16</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>61000</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>06/30 11:35:36</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>79000</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2320000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>280899.21</t>
+          <t>2320000</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>208610</t>
+          <t>280899.21</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>280899</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>72289.21</t>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0.21</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-2026-06-30.xlsx
+++ b/bills/JXZFSP/-5560922286/a04009deb7e69570bc9f5ca765210e487e41c38d8e120e2341bfe7056a39f72d/bill-2026-06-30.xlsx
@@ -13,7 +13,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>群组：金鑫供大牛全国取现</t>
+          <t>群组：金鑫供大牛全国取现DD</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
